--- a/Result/profitability/3017.xlsx
+++ b/Result/profitability/3017.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>10.2075</v>
+        <v>12.50125</v>
       </c>
       <c r="N2" t="n">
-        <v>24.5025</v>
+        <v>25.63625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.63</v>
       </c>
       <c r="M3" t="n">
-        <v>9.53375</v>
+        <v>11.82125</v>
       </c>
       <c r="N3" t="n">
-        <v>23.42625</v>
+        <v>24.37375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>8.857500000000002</v>
+        <v>10.86875</v>
       </c>
       <c r="N4" t="n">
-        <v>22.35</v>
+        <v>23.1925</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.39</v>
       </c>
       <c r="M5" t="n">
-        <v>7.871250000000001</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>20.6575</v>
+        <v>21.6775</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.49</v>
       </c>
       <c r="M6" t="n">
-        <v>6.645</v>
+        <v>7.982500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>19.49</v>
+        <v>20.29625</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.8</v>
       </c>
       <c r="M7" t="n">
-        <v>5.036250000000001</v>
+        <v>5.956250000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>18.57</v>
+        <v>19.3425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.83</v>
       </c>
       <c r="M8" t="n">
-        <v>3.01375</v>
+        <v>3.53875</v>
       </c>
       <c r="N8" t="n">
-        <v>17.62375</v>
+        <v>17.97375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>49121</v>
+      </c>
+      <c r="D75" t="n">
+        <v>33122</v>
+      </c>
+      <c r="E75" t="n">
+        <v>15999</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="G75" t="n">
+        <v>13478</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>27.44%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>457</v>
+      </c>
+      <c r="J75" t="n">
+        <v>13935</v>
+      </c>
+      <c r="K75" t="n">
+        <v>9567</v>
+      </c>
+      <c r="L75" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="M75" t="n">
+        <v>13.23625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>26.6975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>4.199999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2082300446207237</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.800000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09405441719852203</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.366019417475728</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.334289225727161</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
